--- a/test-cases-reports/vulnerability-testing/vulnerability_security_report.xlsx
+++ b/test-cases-reports/vulnerability-testing/vulnerability_security_report.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="524">
   <si>
     <t>🛡️  CAMPUS MENTOR – VULNERABILITY SECURITY ASSESSMENT REPORT</t>
   </si>
   <si>
-    <t>Static Security Analysis  |  Thursday, 18 June 2026  |  8:33:45 pm</t>
+    <t>Static Security Analysis  |  Friday, 19 June 2026  |  5:02:37 am</t>
   </si>
   <si>
     <t>SECURITY SCORE: 83%  |  100 PASS  |  2 FAIL  |  18 WARN  |  120 TOTAL CHECKS</t>
@@ -57,13 +57,13 @@
     <t>Test Date</t>
   </si>
   <si>
-    <t>18/6/2026</t>
+    <t>19/6/2026</t>
   </si>
   <si>
     <t>Test Time</t>
   </si>
   <si>
-    <t>8:33:45 pm</t>
+    <t>5:02:37 am</t>
   </si>
   <si>
     <t>Tester</t>
@@ -184,9 +184,6 @@
   </si>
   <si>
     <t>API keys only found in expected firebase_options.dart</t>
-  </si>
-  <si>
-    <t>8:33:44 pm</t>
   </si>
   <si>
     <t>TC002</t>
@@ -2766,18 +2763,18 @@
         <v>55</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>52</v>
@@ -2789,47 +2786,47 @@
         <v>54</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>63</v>
-      </c>
       <c r="H5" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>52</v>
@@ -2841,73 +2838,73 @@
         <v>54</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>69</v>
-      </c>
       <c r="H7" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>72</v>
-      </c>
       <c r="H8" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>52</v>
@@ -2919,21 +2916,21 @@
         <v>54</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>52</v>
@@ -2945,47 +2942,47 @@
         <v>54</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>81</v>
-      </c>
       <c r="H11" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>52</v>
@@ -2997,203 +2994,203 @@
         <v>54</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>87</v>
-      </c>
       <c r="H13" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="E14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="H14" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="22" t="s">
+      <c r="F15" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="G15" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>96</v>
-      </c>
       <c r="H15" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>99</v>
-      </c>
       <c r="H16" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>102</v>
-      </c>
       <c r="H17" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="19" t="s">
+      <c r="G18" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="G18" s="19" t="s">
-        <v>106</v>
-      </c>
       <c r="H18" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D19" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="16" t="s">
+      <c r="F19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>110</v>
-      </c>
       <c r="H19" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>52</v>
@@ -3205,73 +3202,73 @@
         <v>54</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>116</v>
-      </c>
       <c r="H21" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="E22" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="19" t="s">
+      <c r="G22" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="19" t="s">
-        <v>121</v>
-      </c>
       <c r="H22" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>52</v>
@@ -3283,21 +3280,21 @@
         <v>54</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>52</v>
@@ -3309,73 +3306,73 @@
         <v>54</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>130</v>
-      </c>
       <c r="H25" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D26" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>133</v>
-      </c>
       <c r="H26" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D27" s="16" t="s">
         <v>52</v>
@@ -3387,1555 +3384,1555 @@
         <v>54</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B28" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>139</v>
-      </c>
       <c r="H28" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>142</v>
-      </c>
       <c r="H29" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D30" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H30" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C31" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>148</v>
-      </c>
       <c r="H31" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B32" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C32" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>151</v>
-      </c>
       <c r="H32" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C33" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>154</v>
-      </c>
       <c r="H33" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B34" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C34" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="D34" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>157</v>
-      </c>
       <c r="H34" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C35" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D35" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>160</v>
-      </c>
       <c r="H35" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B36" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D36" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>163</v>
-      </c>
       <c r="H36" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F37" s="15" t="s">
+      <c r="G37" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="G37" s="15" t="s">
-        <v>167</v>
-      </c>
       <c r="H37" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C38" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="D38" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>170</v>
-      </c>
       <c r="H38" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C39" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>173</v>
-      </c>
       <c r="H39" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B40" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C40" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="D40" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>176</v>
-      </c>
       <c r="H40" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C41" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G41" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="D41" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G41" s="15" t="s">
-        <v>179</v>
-      </c>
       <c r="H41" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B42" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C42" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F42" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="D42" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" s="19" t="s">
+      <c r="G42" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="G42" s="19" t="s">
-        <v>183</v>
-      </c>
       <c r="H42" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G43" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D43" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G43" s="15" t="s">
-        <v>186</v>
-      </c>
       <c r="H43" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B44" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G44" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="D44" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>189</v>
-      </c>
       <c r="H44" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="D45" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G45" s="15" t="s">
-        <v>192</v>
-      </c>
       <c r="H45" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B46" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G46" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="D46" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>195</v>
-      </c>
       <c r="H46" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C47" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G47" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="D47" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G47" s="15" t="s">
-        <v>198</v>
-      </c>
       <c r="H47" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B48" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="D48" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>201</v>
-      </c>
       <c r="H48" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G49" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="D49" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G49" s="15" t="s">
-        <v>204</v>
-      </c>
       <c r="H49" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B50" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G50" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="D50" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>207</v>
-      </c>
       <c r="H50" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G51" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="D51" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E51" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G51" s="15" t="s">
-        <v>210</v>
-      </c>
       <c r="H51" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B52" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G52" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="D52" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G52" s="19" t="s">
-        <v>213</v>
-      </c>
       <c r="H52" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G53" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="D53" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G53" s="15" t="s">
-        <v>216</v>
-      </c>
       <c r="H53" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B54" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G54" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="D54" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G54" s="19" t="s">
-        <v>219</v>
-      </c>
       <c r="H54" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G55" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D55" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G55" s="15" t="s">
-        <v>222</v>
-      </c>
       <c r="H55" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B56" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C56" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G56" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="D56" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G56" s="19" t="s">
-        <v>225</v>
-      </c>
       <c r="H56" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G57" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D57" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G57" s="15" t="s">
-        <v>228</v>
-      </c>
       <c r="H57" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G58" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="D58" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F58" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G58" s="19" t="s">
-        <v>231</v>
-      </c>
       <c r="H58" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G59" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="D59" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F59" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G59" s="15" t="s">
-        <v>234</v>
-      </c>
       <c r="H59" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B60" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G60" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F60" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G60" s="19" t="s">
-        <v>237</v>
-      </c>
       <c r="H60" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D61" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G61" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="D61" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G61" s="15" t="s">
-        <v>240</v>
-      </c>
       <c r="H61" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B62" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="D62" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G62" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="D62" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G62" s="19" t="s">
-        <v>243</v>
-      </c>
       <c r="H62" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C63" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G63" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="D63" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E63" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G63" s="15" t="s">
-        <v>246</v>
-      </c>
       <c r="H63" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B64" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C64" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F64" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="D64" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E64" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>249</v>
-      </c>
       <c r="G64" s="19" t="s">
         <v>54</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C65" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F65" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="D65" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E65" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F65" s="15" t="s">
+      <c r="G65" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="G65" s="15" t="s">
-        <v>253</v>
-      </c>
       <c r="H65" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B66" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C66" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F66" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="D66" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E66" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F66" s="19" t="s">
+      <c r="G66" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="G66" s="19" t="s">
-        <v>257</v>
-      </c>
       <c r="H66" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C67" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G67" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="D67" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F67" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G67" s="15" t="s">
-        <v>260</v>
-      </c>
       <c r="H67" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B68" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C68" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F68" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="D68" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E68" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F68" s="19" t="s">
+      <c r="G68" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="G68" s="19" t="s">
-        <v>264</v>
-      </c>
       <c r="H68" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C69" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D69" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G69" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="D69" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E69" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F69" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G69" s="15" t="s">
-        <v>267</v>
-      </c>
       <c r="H69" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B70" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C70" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="D70" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F70" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G70" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="D70" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G70" s="19" t="s">
-        <v>270</v>
-      </c>
       <c r="H70" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C71" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G71" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="D71" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E71" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G71" s="15" t="s">
-        <v>273</v>
-      </c>
       <c r="H71" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B72" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C72" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G72" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="D72" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E72" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G72" s="19" t="s">
-        <v>276</v>
-      </c>
       <c r="H72" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C73" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G73" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="D73" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E73" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F73" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G73" s="15" t="s">
-        <v>279</v>
-      </c>
       <c r="H73" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B74" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C74" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G74" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="D74" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E74" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F74" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G74" s="19" t="s">
-        <v>282</v>
-      </c>
       <c r="H74" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C75" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="D75" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G75" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="D75" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E75" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F75" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G75" s="15" t="s">
-        <v>285</v>
-      </c>
       <c r="H75" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B76" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C76" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E76" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G76" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D76" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E76" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F76" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G76" s="19" t="s">
-        <v>288</v>
-      </c>
       <c r="H76" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C77" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="D77" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E77" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G77" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="D77" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E77" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F77" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G77" s="15" t="s">
-        <v>291</v>
-      </c>
       <c r="H77" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B78" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C78" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="D78" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E78" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G78" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="D78" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E78" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F78" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G78" s="19" t="s">
-        <v>294</v>
-      </c>
       <c r="H78" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C79" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="D79" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E79" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F79" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G79" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="D79" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E79" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F79" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G79" s="15" t="s">
-        <v>297</v>
-      </c>
       <c r="H79" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B80" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C80" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="D80" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G80" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="D80" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E80" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F80" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G80" s="19" t="s">
-        <v>300</v>
-      </c>
       <c r="H80" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C81" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F81" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G81" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="D81" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E81" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F81" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G81" s="15" t="s">
-        <v>303</v>
-      </c>
       <c r="H81" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B82" s="18" t="s">
         <v>33</v>
       </c>
       <c r="C82" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="D82" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E82" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G82" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="D82" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E82" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F82" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G82" s="19" t="s">
-        <v>306</v>
-      </c>
       <c r="H82" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C83" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="D83" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E83" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G83" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="D83" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E83" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F83" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G83" s="15" t="s">
-        <v>309</v>
-      </c>
       <c r="H83" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B84" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C84" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E84" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G84" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="D84" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E84" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F84" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G84" s="19" t="s">
-        <v>312</v>
-      </c>
       <c r="H84" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C85" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="D85" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E85" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G85" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="D85" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F85" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G85" s="15" t="s">
-        <v>315</v>
-      </c>
       <c r="H85" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="18" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B86" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C86" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E86" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F86" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G86" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="D86" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E86" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F86" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G86" s="19" t="s">
-        <v>318</v>
-      </c>
       <c r="H86" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B87" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D87" s="16" t="s">
         <v>52</v>
@@ -4947,281 +4944,281 @@
         <v>54</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H87" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B88" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C88" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E88" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G88" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="D88" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E88" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F88" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G88" s="19" t="s">
-        <v>324</v>
-      </c>
       <c r="H88" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C89" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="D89" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E89" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G89" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="D89" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E89" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F89" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G89" s="15" t="s">
-        <v>327</v>
-      </c>
       <c r="H89" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B90" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C90" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="D90" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F90" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G90" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="D90" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E90" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F90" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G90" s="19" t="s">
-        <v>330</v>
-      </c>
       <c r="H90" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C91" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="D91" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E91" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F91" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G91" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="D91" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E91" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F91" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G91" s="15" t="s">
-        <v>333</v>
-      </c>
       <c r="H91" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="18" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B92" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C92" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="D92" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E92" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F92" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G92" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="D92" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E92" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F92" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G92" s="19" t="s">
-        <v>336</v>
-      </c>
       <c r="H92" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C93" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E93" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G93" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="D93" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E93" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F93" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G93" s="15" t="s">
-        <v>339</v>
-      </c>
       <c r="H93" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B94" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C94" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E94" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F94" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G94" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="D94" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F94" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G94" s="19" t="s">
-        <v>342</v>
-      </c>
       <c r="H94" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B95" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C95" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="D95" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E95" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F95" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G95" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="D95" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E95" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F95" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G95" s="15" t="s">
-        <v>345</v>
-      </c>
       <c r="H95" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B96" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C96" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="D96" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E96" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F96" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G96" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="D96" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E96" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F96" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G96" s="19" t="s">
-        <v>348</v>
-      </c>
       <c r="H96" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C97" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="D97" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E97" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F97" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G97" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="D97" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E97" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F97" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G97" s="15" t="s">
-        <v>351</v>
-      </c>
       <c r="H97" s="14" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="18" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B98" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D98" s="16" t="s">
         <v>52</v>
@@ -5233,33 +5230,33 @@
         <v>54</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B99" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C99" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="D99" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E99" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F99" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G99" s="15" t="s">
         <v>356</v>
-      </c>
-      <c r="D99" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E99" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F99" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G99" s="15" t="s">
-        <v>357</v>
       </c>
       <c r="H99" s="14" t="s">
         <v>15</v>
@@ -5267,25 +5264,25 @@
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B100" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C100" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="D100" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E100" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F100" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G100" s="19" t="s">
         <v>359</v>
-      </c>
-      <c r="D100" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E100" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F100" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G100" s="19" t="s">
-        <v>360</v>
       </c>
       <c r="H100" s="18" t="s">
         <v>15</v>
@@ -5293,25 +5290,25 @@
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B101" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C101" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="D101" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E101" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G101" s="15" t="s">
         <v>362</v>
-      </c>
-      <c r="D101" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E101" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F101" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G101" s="15" t="s">
-        <v>363</v>
       </c>
       <c r="H101" s="14" t="s">
         <v>15</v>
@@ -5319,25 +5316,25 @@
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B102" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C102" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="D102" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E102" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F102" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G102" s="19" t="s">
         <v>365</v>
-      </c>
-      <c r="D102" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E102" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F102" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G102" s="19" t="s">
-        <v>366</v>
       </c>
       <c r="H102" s="18" t="s">
         <v>15</v>
@@ -5345,25 +5342,25 @@
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C103" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="D103" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E103" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G103" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="D103" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E103" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F103" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G103" s="15" t="s">
-        <v>369</v>
       </c>
       <c r="H103" s="14" t="s">
         <v>15</v>
@@ -5371,25 +5368,25 @@
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="18" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B104" s="18" t="s">
         <v>37</v>
       </c>
       <c r="C104" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="D104" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E104" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F104" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G104" s="19" t="s">
         <v>371</v>
-      </c>
-      <c r="D104" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E104" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F104" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G104" s="19" t="s">
-        <v>372</v>
       </c>
       <c r="H104" s="18" t="s">
         <v>15</v>
@@ -5397,25 +5394,25 @@
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C105" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E105" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F105" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G105" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="D105" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E105" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F105" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G105" s="15" t="s">
-        <v>375</v>
       </c>
       <c r="H105" s="14" t="s">
         <v>15</v>
@@ -5423,25 +5420,25 @@
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="18" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B106" s="18" t="s">
         <v>37</v>
       </c>
       <c r="C106" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E106" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F106" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G106" s="19" t="s">
         <v>377</v>
-      </c>
-      <c r="D106" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E106" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F106" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G106" s="19" t="s">
-        <v>378</v>
       </c>
       <c r="H106" s="18" t="s">
         <v>15</v>
@@ -5449,25 +5446,25 @@
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B107" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C107" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="D107" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E107" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G107" s="15" t="s">
         <v>380</v>
-      </c>
-      <c r="D107" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E107" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F107" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G107" s="15" t="s">
-        <v>381</v>
       </c>
       <c r="H107" s="14" t="s">
         <v>15</v>
@@ -5475,25 +5472,25 @@
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="18" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B108" s="18" t="s">
         <v>37</v>
       </c>
       <c r="C108" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="D108" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E108" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F108" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G108" s="19" t="s">
         <v>383</v>
-      </c>
-      <c r="D108" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E108" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F108" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G108" s="19" t="s">
-        <v>384</v>
       </c>
       <c r="H108" s="18" t="s">
         <v>15</v>
@@ -5501,25 +5498,25 @@
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C109" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="D109" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E109" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F109" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G109" s="15" t="s">
         <v>386</v>
-      </c>
-      <c r="D109" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E109" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F109" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G109" s="15" t="s">
-        <v>387</v>
       </c>
       <c r="H109" s="14" t="s">
         <v>15</v>
@@ -5527,25 +5524,25 @@
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="18" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B110" s="18" t="s">
         <v>37</v>
       </c>
       <c r="C110" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="D110" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E110" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F110" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G110" s="19" t="s">
         <v>389</v>
-      </c>
-      <c r="D110" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E110" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F110" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G110" s="19" t="s">
-        <v>390</v>
       </c>
       <c r="H110" s="18" t="s">
         <v>15</v>
@@ -5553,16 +5550,16 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B111" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D111" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E111" s="17" t="s">
         <v>53</v>
@@ -5571,7 +5568,7 @@
         <v>54</v>
       </c>
       <c r="G111" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H111" s="14" t="s">
         <v>15</v>
@@ -5579,25 +5576,25 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="18" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B112" s="18" t="s">
         <v>37</v>
       </c>
       <c r="C112" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="D112" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E112" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F112" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G112" s="19" t="s">
         <v>394</v>
-      </c>
-      <c r="D112" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E112" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F112" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G112" s="19" t="s">
-        <v>395</v>
       </c>
       <c r="H112" s="18" t="s">
         <v>15</v>
@@ -5605,25 +5602,25 @@
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B113" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C113" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E113" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G113" s="15" t="s">
         <v>397</v>
-      </c>
-      <c r="D113" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E113" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F113" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G113" s="15" t="s">
-        <v>398</v>
       </c>
       <c r="H113" s="14" t="s">
         <v>15</v>
@@ -5631,25 +5628,25 @@
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="18" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B114" s="18" t="s">
         <v>39</v>
       </c>
       <c r="C114" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="D114" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E114" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F114" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G114" s="19" t="s">
         <v>400</v>
-      </c>
-      <c r="D114" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E114" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F114" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G114" s="19" t="s">
-        <v>401</v>
       </c>
       <c r="H114" s="18" t="s">
         <v>15</v>
@@ -5657,25 +5654,25 @@
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B115" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C115" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="D115" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E115" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F115" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G115" s="15" t="s">
         <v>403</v>
-      </c>
-      <c r="D115" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E115" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F115" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G115" s="15" t="s">
-        <v>404</v>
       </c>
       <c r="H115" s="14" t="s">
         <v>15</v>
@@ -5683,25 +5680,25 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="18" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B116" s="18" t="s">
         <v>39</v>
       </c>
       <c r="C116" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="D116" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E116" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F116" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G116" s="19" t="s">
         <v>406</v>
-      </c>
-      <c r="D116" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E116" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F116" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G116" s="19" t="s">
-        <v>407</v>
       </c>
       <c r="H116" s="18" t="s">
         <v>15</v>
@@ -5709,25 +5706,25 @@
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B117" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C117" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E117" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F117" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G117" s="15" t="s">
         <v>409</v>
-      </c>
-      <c r="D117" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E117" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F117" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G117" s="15" t="s">
-        <v>410</v>
       </c>
       <c r="H117" s="14" t="s">
         <v>15</v>
@@ -5735,25 +5732,25 @@
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B118" s="18" t="s">
         <v>39</v>
       </c>
       <c r="C118" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="D118" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E118" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F118" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G118" s="19" t="s">
         <v>412</v>
-      </c>
-      <c r="D118" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E118" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F118" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G118" s="19" t="s">
-        <v>413</v>
       </c>
       <c r="H118" s="18" t="s">
         <v>15</v>
@@ -5761,25 +5758,25 @@
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C119" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="D119" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E119" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F119" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G119" s="15" t="s">
         <v>415</v>
-      </c>
-      <c r="D119" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E119" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F119" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G119" s="15" t="s">
-        <v>416</v>
       </c>
       <c r="H119" s="14" t="s">
         <v>15</v>
@@ -5787,25 +5784,25 @@
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B120" s="18" t="s">
         <v>39</v>
       </c>
       <c r="C120" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="D120" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E120" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F120" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G120" s="19" t="s">
         <v>418</v>
-      </c>
-      <c r="D120" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E120" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F120" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G120" s="19" t="s">
-        <v>419</v>
       </c>
       <c r="H120" s="18" t="s">
         <v>15</v>
@@ -5813,25 +5810,25 @@
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B121" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C121" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E121" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F121" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G121" s="15" t="s">
         <v>421</v>
-      </c>
-      <c r="D121" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E121" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F121" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G121" s="15" t="s">
-        <v>422</v>
       </c>
       <c r="H121" s="14" t="s">
         <v>15</v>
@@ -5839,25 +5836,25 @@
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B122" s="18" t="s">
         <v>39</v>
       </c>
       <c r="C122" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="D122" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E122" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F122" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G122" s="19" t="s">
         <v>424</v>
-      </c>
-      <c r="D122" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E122" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F122" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G122" s="19" t="s">
-        <v>425</v>
       </c>
       <c r="H122" s="18" t="s">
         <v>15</v>
@@ -5888,7 +5885,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -5899,7 +5896,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>43</v>
@@ -5911,13 +5908,13 @@
         <v>47</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>48</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5925,22 +5922,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>108</v>
-      </c>
       <c r="F3" s="26" t="s">
         <v>54</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5948,22 +5945,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>249</v>
-      </c>
       <c r="G4" s="26" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5971,22 +5968,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="22" t="s">
+      <c r="F5" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>95</v>
-      </c>
       <c r="G5" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5994,22 +5991,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="28" t="s">
+      <c r="F6" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="28" t="s">
-        <v>166</v>
-      </c>
       <c r="G6" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6017,22 +6014,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>245</v>
-      </c>
       <c r="F7" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6040,22 +6037,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="28" t="s">
+      <c r="F8" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="F8" s="28" t="s">
-        <v>256</v>
-      </c>
       <c r="G8" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6063,22 +6060,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="28" t="s">
+      <c r="F9" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="F9" s="28" t="s">
-        <v>263</v>
-      </c>
       <c r="G9" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6086,22 +6083,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>266</v>
-      </c>
       <c r="F10" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6109,22 +6106,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>305</v>
-      </c>
       <c r="F11" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6132,22 +6129,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="27" t="s">
+        <v>395</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="28" t="s">
         <v>396</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>397</v>
-      </c>
       <c r="F12" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6155,22 +6152,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="28" t="s">
         <v>402</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>403</v>
-      </c>
       <c r="F13" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6178,22 +6175,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="28" t="s">
         <v>417</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>418</v>
-      </c>
       <c r="F14" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6201,22 +6198,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="28" t="s">
+      <c r="F15" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="28" t="s">
-        <v>105</v>
-      </c>
       <c r="G15" s="28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6224,22 +6221,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" s="28" t="s">
+      <c r="F16" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F16" s="28" t="s">
-        <v>182</v>
-      </c>
       <c r="G16" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6247,22 +6244,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="C17" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="28" t="s">
+      <c r="F17" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>252</v>
-      </c>
       <c r="G17" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6270,22 +6267,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="28" t="s">
         <v>322</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>323</v>
-      </c>
       <c r="F18" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6293,22 +6290,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="27" t="s">
+        <v>398</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="28" t="s">
         <v>399</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>400</v>
-      </c>
       <c r="F19" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6316,22 +6313,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="28" t="s">
         <v>411</v>
       </c>
-      <c r="C20" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>412</v>
-      </c>
       <c r="F20" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6339,22 +6336,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="F21" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>120</v>
-      </c>
       <c r="G21" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6362,22 +6359,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="28" t="s">
         <v>414</v>
       </c>
-      <c r="C22" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>415</v>
-      </c>
       <c r="F22" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -6403,7 +6400,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -6421,10 +6418,10 @@
         <v>46</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -6446,7 +6443,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>27</v>
@@ -6455,32 +6452,32 @@
         <v>52</v>
       </c>
       <c r="D4" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="34" t="s">
         <v>58</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>62</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>27</v>
@@ -6489,49 +6486,49 @@
         <v>52</v>
       </c>
       <c r="D6" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>65</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="32" t="s">
         <v>68</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="34" t="s">
         <v>71</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>27</v>
@@ -6540,15 +6537,15 @@
         <v>52</v>
       </c>
       <c r="D9" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="32" t="s">
         <v>74</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>27</v>
@@ -6557,32 +6554,32 @@
         <v>52</v>
       </c>
       <c r="D10" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="34" t="s">
         <v>77</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="31" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="32" t="s">
         <v>80</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="33" t="s">
         <v>27</v>
@@ -6591,83 +6588,83 @@
         <v>52</v>
       </c>
       <c r="D12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="34" t="s">
         <v>83</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="31" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="32" t="s">
         <v>86</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="33" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="34" t="s">
         <v>90</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B15" s="31" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="32" t="s">
         <v>98</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B16" s="33" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>27</v>
@@ -6676,32 +6673,32 @@
         <v>52</v>
       </c>
       <c r="D17" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="32" t="s">
         <v>112</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="33" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="34" t="s">
         <v>115</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>29</v>
@@ -6710,15 +6707,15 @@
         <v>52</v>
       </c>
       <c r="D19" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="32" t="s">
         <v>123</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>29</v>
@@ -6727,49 +6724,49 @@
         <v>52</v>
       </c>
       <c r="D20" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="34" t="s">
         <v>126</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D21" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="32" t="s">
         <v>129</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B22" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="34" t="s">
         <v>132</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>29</v>
@@ -6778,865 +6775,865 @@
         <v>52</v>
       </c>
       <c r="D23" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="32" t="s">
         <v>135</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B24" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" s="34" t="s">
         <v>138</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" s="32" t="s">
         <v>141</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B26" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D26" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="34" t="s">
         <v>144</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B27" s="31" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D27" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" s="32" t="s">
         <v>147</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B28" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D28" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" s="34" t="s">
         <v>150</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B29" s="31" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>153</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B30" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D30" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="34" t="s">
         <v>156</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>29</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D31" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" s="32" t="s">
         <v>159</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B32" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D32" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32" s="34" t="s">
         <v>162</v>
-      </c>
-      <c r="E32" s="34" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B33" s="31" t="s">
         <v>29</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D33" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E33" s="32" t="s">
         <v>169</v>
-      </c>
-      <c r="E33" s="32" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B34" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D34" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" s="34" t="s">
         <v>172</v>
-      </c>
-      <c r="E34" s="34" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>29</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D35" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" s="32" t="s">
         <v>175</v>
-      </c>
-      <c r="E35" s="32" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B36" s="33" t="s">
         <v>29</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D36" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="E36" s="34" t="s">
         <v>178</v>
-      </c>
-      <c r="E36" s="34" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="31" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D37" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" s="32" t="s">
         <v>185</v>
-      </c>
-      <c r="E37" s="32" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="33" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B38" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D38" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E38" s="34" t="s">
         <v>188</v>
-      </c>
-      <c r="E38" s="34" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D39" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" s="32" t="s">
         <v>191</v>
-      </c>
-      <c r="E39" s="32" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B40" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D40" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="E40" s="34" t="s">
         <v>194</v>
-      </c>
-      <c r="E40" s="34" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D41" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="E41" s="32" t="s">
         <v>197</v>
-      </c>
-      <c r="E41" s="32" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B42" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D42" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="E42" s="34" t="s">
         <v>200</v>
-      </c>
-      <c r="E42" s="34" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B43" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D43" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" s="32" t="s">
         <v>203</v>
-      </c>
-      <c r="E43" s="32" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B44" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D44" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="E44" s="34" t="s">
         <v>206</v>
-      </c>
-      <c r="E44" s="34" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D45" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="E45" s="32" t="s">
         <v>209</v>
-      </c>
-      <c r="E45" s="32" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B46" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D46" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="E46" s="34" t="s">
         <v>212</v>
-      </c>
-      <c r="E46" s="34" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B47" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D47" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="E47" s="32" t="s">
         <v>215</v>
-      </c>
-      <c r="E47" s="32" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B48" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D48" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="E48" s="34" t="s">
         <v>218</v>
-      </c>
-      <c r="E48" s="34" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B49" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D49" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E49" s="32" t="s">
         <v>221</v>
-      </c>
-      <c r="E49" s="32" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B50" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D50" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" s="34" t="s">
         <v>224</v>
-      </c>
-      <c r="E50" s="34" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B51" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D51" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="E51" s="32" t="s">
         <v>227</v>
-      </c>
-      <c r="E51" s="32" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B52" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D52" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="E52" s="34" t="s">
         <v>230</v>
-      </c>
-      <c r="E52" s="34" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="31" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B53" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D53" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E53" s="32" t="s">
         <v>233</v>
-      </c>
-      <c r="E53" s="32" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B54" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D54" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="E54" s="34" t="s">
         <v>236</v>
-      </c>
-      <c r="E54" s="34" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="31" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B55" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D55" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="E55" s="32" t="s">
         <v>239</v>
-      </c>
-      <c r="E55" s="32" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B56" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D56" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="E56" s="34" t="s">
         <v>242</v>
-      </c>
-      <c r="E56" s="34" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B57" s="31" t="s">
         <v>33</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D57" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="E57" s="32" t="s">
         <v>259</v>
-      </c>
-      <c r="E57" s="32" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B58" s="33" t="s">
         <v>33</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D58" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="E58" s="34" t="s">
         <v>269</v>
-      </c>
-      <c r="E58" s="34" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B59" s="31" t="s">
         <v>33</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D59" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E59" s="32" t="s">
         <v>272</v>
-      </c>
-      <c r="E59" s="32" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="33" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B60" s="33" t="s">
         <v>33</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D60" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="E60" s="34" t="s">
         <v>275</v>
-      </c>
-      <c r="E60" s="34" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="31" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B61" s="31" t="s">
         <v>33</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D61" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="E61" s="32" t="s">
         <v>278</v>
-      </c>
-      <c r="E61" s="32" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B62" s="33" t="s">
         <v>33</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D62" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="E62" s="34" t="s">
         <v>281</v>
-      </c>
-      <c r="E62" s="34" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B63" s="31" t="s">
         <v>33</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D63" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="E63" s="32" t="s">
         <v>284</v>
-      </c>
-      <c r="E63" s="32" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B64" s="33" t="s">
         <v>33</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D64" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="E64" s="34" t="s">
         <v>287</v>
-      </c>
-      <c r="E64" s="34" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B65" s="31" t="s">
         <v>33</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D65" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="E65" s="32" t="s">
         <v>290</v>
-      </c>
-      <c r="E65" s="32" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="33" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B66" s="33" t="s">
         <v>33</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D66" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="E66" s="34" t="s">
         <v>293</v>
-      </c>
-      <c r="E66" s="34" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B67" s="31" t="s">
         <v>33</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D67" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="E67" s="32" t="s">
         <v>296</v>
-      </c>
-      <c r="E67" s="32" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B68" s="33" t="s">
         <v>33</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D68" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="E68" s="34" t="s">
         <v>299</v>
-      </c>
-      <c r="E68" s="34" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B69" s="31" t="s">
         <v>33</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D69" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="E69" s="32" t="s">
         <v>302</v>
-      </c>
-      <c r="E69" s="32" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B70" s="33" t="s">
         <v>35</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D70" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="E70" s="34" t="s">
         <v>308</v>
-      </c>
-      <c r="E70" s="34" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="31" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B71" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D71" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="E71" s="32" t="s">
         <v>311</v>
-      </c>
-      <c r="E71" s="32" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B72" s="33" t="s">
         <v>35</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D72" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="E72" s="34" t="s">
         <v>314</v>
-      </c>
-      <c r="E72" s="34" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="31" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D73" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="E73" s="32" t="s">
         <v>317</v>
-      </c>
-      <c r="E73" s="32" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="33" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B74" s="33" t="s">
         <v>35</v>
@@ -7645,168 +7642,168 @@
         <v>52</v>
       </c>
       <c r="D74" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="E74" s="34" t="s">
         <v>320</v>
-      </c>
-      <c r="E74" s="34" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B75" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D75" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="E75" s="32" t="s">
         <v>326</v>
-      </c>
-      <c r="E75" s="32" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="33" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B76" s="33" t="s">
         <v>35</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D76" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="E76" s="34" t="s">
         <v>329</v>
-      </c>
-      <c r="E76" s="34" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="31" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B77" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D77" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="E77" s="32" t="s">
         <v>332</v>
-      </c>
-      <c r="E77" s="32" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="33" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B78" s="33" t="s">
         <v>35</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D78" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="E78" s="34" t="s">
         <v>335</v>
-      </c>
-      <c r="E78" s="34" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="31" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B79" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D79" s="32" t="s">
+        <v>337</v>
+      </c>
+      <c r="E79" s="32" t="s">
         <v>338</v>
-      </c>
-      <c r="E79" s="32" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B80" s="33" t="s">
         <v>35</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D80" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="E80" s="34" t="s">
         <v>341</v>
-      </c>
-      <c r="E80" s="34" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="31" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B81" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D81" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="E81" s="32" t="s">
         <v>344</v>
-      </c>
-      <c r="E81" s="32" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B82" s="33" t="s">
         <v>35</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D82" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="E82" s="34" t="s">
         <v>347</v>
-      </c>
-      <c r="E82" s="34" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="31" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B83" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D83" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="E83" s="32" t="s">
         <v>350</v>
-      </c>
-      <c r="E83" s="32" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B84" s="33" t="s">
         <v>35</v>
@@ -7815,316 +7812,316 @@
         <v>52</v>
       </c>
       <c r="D84" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="E84" s="34" t="s">
         <v>353</v>
-      </c>
-      <c r="E84" s="34" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B85" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D85" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="E85" s="32" t="s">
         <v>356</v>
-      </c>
-      <c r="E85" s="32" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B86" s="33" t="s">
         <v>35</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D86" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="E86" s="34" t="s">
         <v>359</v>
-      </c>
-      <c r="E86" s="34" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B87" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D87" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="E87" s="32" t="s">
         <v>362</v>
-      </c>
-      <c r="E87" s="32" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="33" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B88" s="33" t="s">
         <v>35</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D88" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="E88" s="34" t="s">
         <v>365</v>
-      </c>
-      <c r="E88" s="34" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="31" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B89" s="31" t="s">
         <v>37</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D89" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="E89" s="32" t="s">
         <v>368</v>
-      </c>
-      <c r="E89" s="32" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="33" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B90" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D90" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="E90" s="34" t="s">
         <v>371</v>
-      </c>
-      <c r="E90" s="34" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="31" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B91" s="31" t="s">
         <v>37</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D91" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="E91" s="32" t="s">
         <v>374</v>
-      </c>
-      <c r="E91" s="32" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="33" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B92" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D92" s="34" t="s">
+        <v>376</v>
+      </c>
+      <c r="E92" s="34" t="s">
         <v>377</v>
-      </c>
-      <c r="E92" s="34" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="31" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B93" s="31" t="s">
         <v>37</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D93" s="32" t="s">
+        <v>379</v>
+      </c>
+      <c r="E93" s="32" t="s">
         <v>380</v>
-      </c>
-      <c r="E93" s="32" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B94" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D94" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="E94" s="34" t="s">
         <v>383</v>
-      </c>
-      <c r="E94" s="34" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="31" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B95" s="31" t="s">
         <v>37</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D95" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="E95" s="32" t="s">
         <v>386</v>
-      </c>
-      <c r="E95" s="32" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B96" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D96" s="34" t="s">
+        <v>388</v>
+      </c>
+      <c r="E96" s="34" t="s">
         <v>389</v>
-      </c>
-      <c r="E96" s="34" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="31" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B97" s="31" t="s">
         <v>37</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D97" s="32" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E97" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="33" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B98" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D98" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="E98" s="34" t="s">
         <v>394</v>
-      </c>
-      <c r="E98" s="34" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="31" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B99" s="31" t="s">
         <v>39</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D99" s="32" t="s">
+        <v>405</v>
+      </c>
+      <c r="E99" s="32" t="s">
         <v>406</v>
-      </c>
-      <c r="E99" s="32" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="33" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B100" s="33" t="s">
         <v>39</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D100" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="E100" s="34" t="s">
         <v>409</v>
-      </c>
-      <c r="E100" s="34" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="31" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B101" s="31" t="s">
         <v>39</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D101" s="32" t="s">
+        <v>420</v>
+      </c>
+      <c r="E101" s="32" t="s">
         <v>421</v>
-      </c>
-      <c r="E101" s="32" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="33" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B102" s="33" t="s">
         <v>39</v>
       </c>
       <c r="C102" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D102" s="34" t="s">
+        <v>423</v>
+      </c>
+      <c r="E102" s="34" t="s">
         <v>424</v>
-      </c>
-      <c r="E102" s="34" t="s">
-        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -8150,7 +8147,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -8159,189 +8156,189 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>440</v>
-      </c>
       <c r="E2" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="C3" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>444</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>446</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="C4" s="19" t="s">
         <v>447</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>448</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="C5" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>452</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
+        <v>453</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>454</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="C6" s="19" t="s">
         <v>455</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="D6" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>456</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>458</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="C7" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="D7" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>460</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>462</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="C8" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="D8" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>464</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>466</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="C9" s="15" t="s">
         <v>467</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="D9" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>468</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>470</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="C10" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="D10" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>472</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="C11" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="D11" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="15" t="s">
         <v>477</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>479</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="C12" s="19" t="s">
         <v>480</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="D12" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>481</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>477</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -8377,19 +8374,19 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="B2" s="36" t="s">
         <v>483</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="C2" s="36" t="s">
         <v>484</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="D2" s="36" t="s">
         <v>485</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="E2" s="36" t="s">
         <v>486</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>487</v>
       </c>
       <c r="F2" s="36" t="s">
         <v>47</v>
@@ -8397,242 +8394,242 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
+        <v>487</v>
+      </c>
+      <c r="B3" s="37" t="s">
         <v>488</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="C3" s="37" t="s">
         <v>489</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="D3" s="38" t="s">
         <v>490</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="E3" s="37" t="s">
         <v>491</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="F3" s="37" t="s">
         <v>492</v>
-      </c>
-      <c r="F3" s="37" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
+        <v>487</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>489</v>
-      </c>
       <c r="C4" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>494</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>495</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>496</v>
-      </c>
       <c r="F4" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B5" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="38" t="s">
         <v>497</v>
       </c>
-      <c r="C5" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="D5" s="38" t="s">
+      <c r="E5" s="37" t="s">
         <v>498</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>499</v>
-      </c>
       <c r="F5" s="37" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
+        <v>499</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>500</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>502</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>503</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>504</v>
-      </c>
       <c r="F6" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" s="37" t="s">
         <v>500</v>
       </c>
-      <c r="B7" s="37" t="s">
-        <v>501</v>
-      </c>
       <c r="C7" s="37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D7" s="38" t="s">
+        <v>504</v>
+      </c>
+      <c r="E7" s="37" t="s">
         <v>505</v>
       </c>
-      <c r="E7" s="37" t="s">
-        <v>506</v>
-      </c>
       <c r="F7" s="37" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>500</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>501</v>
-      </c>
       <c r="C8" s="18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D8" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>507</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>508</v>
-      </c>
       <c r="F8" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
+        <v>508</v>
+      </c>
+      <c r="B9" s="37" t="s">
         <v>509</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="C9" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="D9" s="38" t="s">
         <v>510</v>
       </c>
-      <c r="C9" s="37" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="38" t="s">
+      <c r="E9" s="37" t="s">
         <v>511</v>
       </c>
-      <c r="E9" s="37" t="s">
-        <v>512</v>
-      </c>
       <c r="F9" s="37" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>510</v>
-      </c>
       <c r="C10" s="18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
+        <v>508</v>
+      </c>
+      <c r="B11" s="37" t="s">
         <v>509</v>
       </c>
-      <c r="B11" s="37" t="s">
-        <v>510</v>
-      </c>
       <c r="C11" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>515</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="C12" s="18" t="s">
         <v>516</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>517</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>518</v>
-      </c>
       <c r="E12" s="18" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
+        <v>514</v>
+      </c>
+      <c r="B13" s="37" t="s">
         <v>515</v>
       </c>
-      <c r="B13" s="37" t="s">
-        <v>516</v>
-      </c>
       <c r="C13" s="37" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
+        <v>519</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>520</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="C14" s="18" t="s">
         <v>521</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>522</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>523</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>524</v>
-      </c>
       <c r="F14" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
